--- a/public/registrations_export.xlsx
+++ b/public/registrations_export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2235" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="626">
   <si>
     <t>S.No</t>
   </si>
@@ -733,7 +733,19 @@
     <t>ritishbhardwaj18@gmail.com</t>
   </si>
   <si>
-    <t>9549305749</t>
+    <t>09549305749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J C Bose University of Science and Technology </t>
+  </si>
+  <si>
+    <t>1842 SECTOR-9 FARIDABAD</t>
+  </si>
+  <si>
+    <t>19001504015</t>
+  </si>
+  <si>
+    <t>session_-Hg16dk3dvu6pkhFneKOT8LJbz74PIOUOm8T4ivOeisB7YCKdBm6GWrGMUQzFZras-ba9hJPw8nLKrRpmW1qJFMCL7MTDwA0cKO65yXlM-O-ZbO97JgY36A0Uw1n</t>
   </si>
   <si>
     <t xml:space="preserve">Gaurav </t>
@@ -769,171 +781,375 @@
     <t>12/3/2026, 2:31:20 pm</t>
   </si>
   <si>
+    <t>shreyasharma15102006@gmail.com</t>
+  </si>
+  <si>
+    <t>12/3/2026, 2:50:54 pm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shreya kesarwani </t>
+  </si>
+  <si>
+    <t>shreyakesarwani8500@gmail.com</t>
+  </si>
+  <si>
+    <t>9335457150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaipur national university </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sadtm campus, girls hostel,jaipur national university </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R50790 </t>
+  </si>
+  <si>
+    <t>session_can5x0f-BuuNKmqXMpg_NyLBQHjVMD0g2Xd4Pb89qtTzfsZgXTdeo5nH8xARTkTiww0DKhJwhO5Sy9zIcw1ZadERCWjqvnCyBuFlK0HV6aMsUZRYl9rYnzZyQck9</t>
+  </si>
+  <si>
+    <t>Chess (Girls)</t>
+  </si>
+  <si>
+    <t>12/3/2026, 4:32:32 pm</t>
+  </si>
+  <si>
+    <t>Devansh Sharma</t>
+  </si>
+  <si>
+    <t>sharmadevansh41490@gmail.com</t>
+  </si>
+  <si>
+    <t>09729360142</t>
+  </si>
+  <si>
+    <t>Panchwati Calony</t>
+  </si>
+  <si>
+    <t>23021252011</t>
+  </si>
+  <si>
+    <t>session_ygVIqGH2R0KNkv-S0Aq2m2J6Ohvcpor4S3FopCBG3dTU6NechhuL0M6b-iZW5YZnJ6S5CPSs087wlfr0xkbgNCzaGtuFhyI0a9vaEZx9r_mG-Ec362XJzxRkUlfx</t>
+  </si>
+  <si>
+    <t>12/3/2026, 8:09:46 pm</t>
+  </si>
+  <si>
+    <t>Aditi Jhanwar</t>
+  </si>
+  <si>
+    <t>jhanwaraditi45@gmail.com</t>
+  </si>
+  <si>
+    <t>9009101737</t>
+  </si>
+  <si>
+    <t>Jaipur National University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SADTM GIRLS HOSTEL near New RTO office jagatpura Jaipur </t>
+  </si>
+  <si>
+    <t>R53435</t>
+  </si>
+  <si>
+    <t>session_wUYbnjyvfBKnZ0-EOTIwTyRr3Vlvhn1Wc0WRbRSUCrk4bjZT-rcEw1lxXkyfQsryndBOpNBhVHl7X_5XvqRJQYQ6ibZfiaBh21tM_Kz_E-4f3yfq33DuZXHKmSuG</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:07:42 am</t>
+  </si>
+  <si>
+    <t>Spardha Admin</t>
+  </si>
+  <si>
+    <t>spardha@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>F_RYAAAjB</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:14:02 am</t>
+  </si>
+  <si>
+    <t>Garv Shamra</t>
+  </si>
+  <si>
+    <t>garvtalin@gmail.com</t>
+  </si>
+  <si>
+    <t>7852865011</t>
+  </si>
+  <si>
+    <t>JK Lakshmipat University</t>
+  </si>
+  <si>
+    <t>6777/27 b , Ramganj, 677/27 b ramganj</t>
+  </si>
+  <si>
+    <t>2024BTech029 l</t>
+  </si>
+  <si>
+    <t>session_DJ_AWePfYcsghXrnyB9IhFqWV_CuPVHVMz_h1Fw59gzz2MlzIvL4ma8l8XBlBVORtKfc5YkR3jLimMOJ5GdcWUhNSnkgZYoUxlkVbIPtOY2hTm_qgOWmI97TM5mM</t>
+  </si>
+  <si>
+    <t>14/3/2026, 3:30:21 pm</t>
+  </si>
+  <si>
+    <t>Yash</t>
+  </si>
+  <si>
+    <t>yashbansal531@gmail.com</t>
+  </si>
+  <si>
+    <t>8619011601</t>
+  </si>
+  <si>
+    <t>JKLU</t>
+  </si>
+  <si>
+    <t>jaipuria</t>
+  </si>
+  <si>
+    <t>2024BTEch128</t>
+  </si>
+  <si>
+    <t>session_xOODT6j4eLobsb9EcagQ9T9-4uLeXYjlov2gGofe91lAmLLmgyJi8UwPZAQ-o6IuODF9LUgKcjxnWl0XF7cRku_ceZQfzp6jnIgbcymHxnZomHWk3LL7c4LKoTT9</t>
+  </si>
+  <si>
+    <t>14/3/2026, 3:46:41 pm</t>
+  </si>
+  <si>
+    <t>AARADHY SHIV SHUKLA</t>
+  </si>
+  <si>
+    <t>shivaaradhy@gmail.com</t>
+  </si>
+  <si>
+    <t>8423251554</t>
+  </si>
+  <si>
+    <t>JNUIMSRC</t>
+  </si>
+  <si>
+    <t>JNU MEDICAL COLLEGE, JAGATPURA</t>
+  </si>
+  <si>
+    <t>25M0154</t>
+  </si>
+  <si>
+    <t>session_EQGFQy-9KzkYgWBwL8I9mi_Y7WM7XaOJqR_GZQvb2ySUGocxfoVYUc4QmSy0QEWGVbx5hyxWxJGCJKbu0YotT26kboioJtszcD4Y8I9L8ya06JEoS1wrTkgFY3cZ</t>
+  </si>
+  <si>
+    <t>Football (7v7) (Boys)</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:14:12 pm</t>
+  </si>
+  <si>
+    <t>Abhinav Dhankhar</t>
+  </si>
+  <si>
+    <t>abhinavdhankar100@gmail.com</t>
+  </si>
+  <si>
+    <t>8295383138</t>
+  </si>
+  <si>
+    <t>JNU Medical College, Jagatpura</t>
+  </si>
+  <si>
+    <t>25M0155</t>
+  </si>
+  <si>
+    <t>session_S_q-7ALggHWdZY2t0kYXEnAddn0As7-toBQbYlRqqMLzT8uCyDRuSaaE9tIsm3NBIUELP15Up61dWmfReEtJ4Br3_-BU5gvGg_lek5tu9n25L8CiHfjuLNJmT8QP</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:14:37 pm</t>
+  </si>
+  <si>
+    <t>Jay Chauhan</t>
+  </si>
+  <si>
+    <t>chauhanj749@gmail.com</t>
+  </si>
+  <si>
+    <t>9643875103</t>
+  </si>
+  <si>
+    <t>C 302 mahima belle vista</t>
+  </si>
+  <si>
+    <t>Ms_1152</t>
+  </si>
+  <si>
+    <t>session_TGTCfqgVG5qTSYYtKMyWrHAwOJTasTBj6kac5lpp3CxnW_M3lQ6mudbuJ7jfnrwK5hOPwLXJkR3zp_IX3L1rP_xFlsf2yTNUGRTN6rRI6EXYIIB4-mDV9pN_fJ89</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:45:51 pm</t>
+  </si>
+  <si>
+    <t>Joy</t>
+  </si>
+  <si>
+    <t>joydulani@gmail.com</t>
+  </si>
+  <si>
+    <t>9399188716</t>
+  </si>
+  <si>
+    <t>Mahima bellevista</t>
+  </si>
+  <si>
+    <t>MS123</t>
+  </si>
+  <si>
+    <t>session_xPh-JQsKgadwaqye5crf2EWa6HKubtxzioum51K1tOPpXAFgHcn97bprbYREk2gjXoqxbva0dl6D9yA6Ns4JV8UIocS2j9900tJA86a_kZMKlH44crR3PQCg1Lnp</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:46:05 pm</t>
+  </si>
+  <si>
+    <t>VISHAL YADAV</t>
+  </si>
+  <si>
+    <t>vy641468@gmail.com</t>
+  </si>
+  <si>
+    <t>7522010377</t>
+  </si>
+  <si>
+    <t>JAIPUR NATIONAL UNIVERSITY ISTITUTE FOR MEDICAL SCIENCES &amp; RESEARCH CENTRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vrinda Gardens </t>
+  </si>
+  <si>
+    <t>JNU_MS1242</t>
+  </si>
+  <si>
+    <t>session_kEMt9I1BGERV8bOr7bVMgVGVzOYewRX5AeayHfGXBB1roccMGoicfMpu0nqeQEh5ibq3PCkTfsEHeifn0eMWExY-RnJkAZ4JSq1OB95P8jBaTgFcr4kjVz1a-aAP</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:14:38 pm</t>
+  </si>
+  <si>
+    <t>Test Fix User</t>
+  </si>
+  <si>
+    <t>test_fix_1773672994754@example.com</t>
+  </si>
+  <si>
+    <t>TEST_TXN_123</t>
+  </si>
+  <si>
+    <t>16/3/2026, 8:26:35 pm</t>
+  </si>
+  <si>
+    <t>Event</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Team Name</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>Leader</t>
+  </si>
+  <si>
+    <t>Purvee Dudheria's Team</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Archita Bhargava's Team</t>
+  </si>
+  <si>
+    <t>RISHABH SHARMA's Team</t>
+  </si>
+  <si>
+    <t>Ashok kumar's Team</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Amount (₹)</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>test_fix_1773672994754</t>
+  </si>
+  <si>
+    <t>22/2/2026, 6:17:12 pm</t>
+  </si>
+  <si>
+    <t>test_fix_1773672953633</t>
+  </si>
+  <si>
+    <t>test_fix_1773672953633@example.com</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>order_13c528dc980e</t>
+  </si>
+  <si>
+    <t>order_dc9a40e23a64</t>
+  </si>
+  <si>
+    <t>shlok chaturvedi</t>
+  </si>
+  <si>
+    <t>shlokchaturvedi@jklu.edu.in</t>
+  </si>
+  <si>
+    <t>07737257861</t>
+  </si>
+  <si>
+    <t>jklu</t>
+  </si>
+  <si>
+    <t>F-2, K-4 Ramnagar sodala extension near green field school jaipur</t>
+  </si>
+  <si>
+    <t>2565233</t>
+  </si>
+  <si>
+    <t>Football (5v5) (Girls), Basketball (Boys)</t>
+  </si>
+  <si>
+    <t>22/2/2026, 9:12:47 pm</t>
+  </si>
+  <si>
+    <t>order_b40680149159</t>
+  </si>
+  <si>
+    <t>23/2/2026, 9:46:45 am</t>
+  </si>
+  <si>
+    <t>order_95a81276d2c1</t>
+  </si>
+  <si>
     <t>Yash Bansal</t>
   </si>
   <si>
-    <t>yashbansal531@gmail.com</t>
-  </si>
-  <si>
-    <t>8619011601</t>
-  </si>
-  <si>
-    <t>JKLU</t>
-  </si>
-  <si>
-    <t>6777/27 b , Ramganj, 677/27 b ramganj</t>
-  </si>
-  <si>
     <t>2024Btech128</t>
   </si>
   <si>
-    <t>session_xOODT6j4eLobsb9EcagQ9T9-4uLeXYjlov2gGofe91lAmLLmgyJi8UwPZAQ-o6IuODF9LUgKcjxnWl0XF7cRku_ceZQfzp6jnIgbcymHxnZomHWk3LL7c4LKoTT9</t>
-  </si>
-  <si>
-    <t>Chess (Girls)</t>
-  </si>
-  <si>
-    <t>12/3/2026, 2:50:53 pm</t>
-  </si>
-  <si>
-    <t>shreyasharma15102006@gmail.com</t>
-  </si>
-  <si>
-    <t>12/3/2026, 2:50:54 pm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shreya kesarwani </t>
-  </si>
-  <si>
-    <t>shreyakesarwani8500@gmail.com</t>
-  </si>
-  <si>
-    <t>9335457150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaipur national university </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sadtm campus, girls hostel,jaipur national university </t>
-  </si>
-  <si>
-    <t xml:space="preserve">R50790 </t>
-  </si>
-  <si>
-    <t>session_can5x0f-BuuNKmqXMpg_NyLBQHjVMD0g2Xd4Pb89qtTzfsZgXTdeo5nH8xARTkTiww0DKhJwhO5Sy9zIcw1ZadERCWjqvnCyBuFlK0HV6aMsUZRYl9rYnzZyQck9</t>
-  </si>
-  <si>
-    <t>12/3/2026, 4:32:32 pm</t>
-  </si>
-  <si>
-    <t>Devansh Sharma</t>
-  </si>
-  <si>
-    <t>sharmadevansh41490@gmail.com</t>
-  </si>
-  <si>
-    <t>09729360142</t>
-  </si>
-  <si>
-    <t>Panchwati Calony</t>
-  </si>
-  <si>
-    <t>23021252011</t>
-  </si>
-  <si>
-    <t>session_ygVIqGH2R0KNkv-S0Aq2m2J6Ohvcpor4S3FopCBG3dTU6NechhuL0M6b-iZW5YZnJ6S5CPSs087wlfr0xkbgNCzaGtuFhyI0a9vaEZx9r_mG-Ec362XJzxRkUlfx</t>
-  </si>
-  <si>
-    <t>12/3/2026, 8:09:46 pm</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Team Name</t>
-  </si>
-  <si>
-    <t>Individual</t>
-  </si>
-  <si>
-    <t>Leader</t>
-  </si>
-  <si>
-    <t>Purvee Dudheria's Team</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Archita Bhargava's Team</t>
-  </si>
-  <si>
-    <t>RISHABH SHARMA's Team</t>
-  </si>
-  <si>
-    <t>Ashok kumar's Team</t>
-  </si>
-  <si>
-    <t>Order ID</t>
-  </si>
-  <si>
-    <t>Events</t>
-  </si>
-  <si>
-    <t>Amount (₹)</t>
-  </si>
-  <si>
-    <t>Payment Date</t>
-  </si>
-  <si>
-    <t>order_13c528dc980e</t>
-  </si>
-  <si>
-    <t>pending</t>
-  </si>
-  <si>
-    <t>22/2/2026, 6:17:12 pm</t>
-  </si>
-  <si>
-    <t>order_dc9a40e23a64</t>
-  </si>
-  <si>
-    <t>shlok chaturvedi</t>
-  </si>
-  <si>
-    <t>shlokchaturvedi@jklu.edu.in</t>
-  </si>
-  <si>
-    <t>07737257861</t>
-  </si>
-  <si>
-    <t>jklu</t>
-  </si>
-  <si>
-    <t>F-2, K-4 Ramnagar sodala extension near green field school jaipur</t>
-  </si>
-  <si>
-    <t>2565233</t>
-  </si>
-  <si>
-    <t>Football (5v5) (Girls), Basketball (Boys)</t>
-  </si>
-  <si>
-    <t>22/2/2026, 9:12:47 pm</t>
-  </si>
-  <si>
-    <t>order_b40680149159</t>
-  </si>
-  <si>
-    <t>23/2/2026, 9:46:45 am</t>
-  </si>
-  <si>
-    <t>order_95a81276d2c1</t>
-  </si>
-  <si>
     <t>23/2/2026, 4:26:52 pm</t>
   </si>
   <si>
@@ -1360,24 +1576,6 @@
     <t>order_c6cd3f0537de</t>
   </si>
   <si>
-    <t>Aditi Jhanwar</t>
-  </si>
-  <si>
-    <t>jhanwaraditi45@gmail.com</t>
-  </si>
-  <si>
-    <t>9009101737</t>
-  </si>
-  <si>
-    <t>Jaipur National University</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SADTM GIRLS HOSTEL near New RTO office jagatpura Jaipur </t>
-  </si>
-  <si>
-    <t>R53435</t>
-  </si>
-  <si>
     <t>12/3/2026, 3:47:25 pm</t>
   </si>
   <si>
@@ -1439,6 +1637,186 @@
   </si>
   <si>
     <t>12/3/2026, 10:51:41 pm</t>
+  </si>
+  <si>
+    <t>order_513deb5d360c</t>
+  </si>
+  <si>
+    <t>13/3/2026, 1:45:06 pm</t>
+  </si>
+  <si>
+    <t>order_b65d7dd1c59e</t>
+  </si>
+  <si>
+    <t>Yashveer Singh chouhan</t>
+  </si>
+  <si>
+    <t>yashveersinghchouhan03@gmail.com</t>
+  </si>
+  <si>
+    <t>8769276296</t>
+  </si>
+  <si>
+    <t>Skit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skit </t>
+  </si>
+  <si>
+    <t>Eskcs854</t>
+  </si>
+  <si>
+    <t>13/3/2026, 9:28:26 pm</t>
+  </si>
+  <si>
+    <t>order_2ffc62c61662</t>
+  </si>
+  <si>
+    <t>14/3/2026, 9:17:51 am</t>
+  </si>
+  <si>
+    <t>order_6319d5ad8801</t>
+  </si>
+  <si>
+    <t>yshbansal05@gmail.com</t>
+  </si>
+  <si>
+    <t>14/3/2026, 9:34:34 am</t>
+  </si>
+  <si>
+    <t>order_27d58d82138c</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:07:07 am</t>
+  </si>
+  <si>
+    <t>order_17bcf6f18846</t>
+  </si>
+  <si>
+    <t>Prateek Saxena</t>
+  </si>
+  <si>
+    <t>pksaxena6453@gmail.com</t>
+  </si>
+  <si>
+    <t>9414307390</t>
+  </si>
+  <si>
+    <t>Plot No 132, Suraj Nagar</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:31:51 am</t>
+  </si>
+  <si>
+    <t>order_a9208f87af91</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:33:58 am</t>
+  </si>
+  <si>
+    <t>order_6104aff87895</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:35:21 am</t>
+  </si>
+  <si>
+    <t>order_d719eafd4ef5</t>
+  </si>
+  <si>
+    <t>RITISH BHARDWAJ</t>
+  </si>
+  <si>
+    <t>14/3/2026, 2:01:46 pm</t>
+  </si>
+  <si>
+    <t>order_3a212898402a</t>
+  </si>
+  <si>
+    <t>Prakhar Pandey</t>
+  </si>
+  <si>
+    <t>prakhar7327@gmail.com</t>
+  </si>
+  <si>
+    <t>7073092330</t>
+  </si>
+  <si>
+    <t>Jnu medical hospital jagatpura</t>
+  </si>
+  <si>
+    <t>823678</t>
+  </si>
+  <si>
+    <t>14/3/2026, 2:51:50 pm</t>
+  </si>
+  <si>
+    <t>order_beef420fffa3</t>
+  </si>
+  <si>
+    <t>14/3/2026, 3:29:28 pm</t>
+  </si>
+  <si>
+    <t>order_7de43a6922eb</t>
+  </si>
+  <si>
+    <t>14/3/2026, 3:40:44 pm</t>
+  </si>
+  <si>
+    <t>order_67ccfc325971</t>
+  </si>
+  <si>
+    <t>14/3/2026, 3:46:10 pm</t>
+  </si>
+  <si>
+    <t>order_31fb591d506f</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:11:23 pm</t>
+  </si>
+  <si>
+    <t>order_02478534ea45</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:12:44 pm</t>
+  </si>
+  <si>
+    <t>order_45d578a1a831</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:13:16 pm</t>
+  </si>
+  <si>
+    <t>order_c91db97fcf62</t>
+  </si>
+  <si>
+    <t>14/3/2026, 7:14:02 pm</t>
+  </si>
+  <si>
+    <t>order_5e28e7edac22</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:45:00 pm</t>
+  </si>
+  <si>
+    <t>order_cfbb5490efd7</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:45:23 pm</t>
+  </si>
+  <si>
+    <t>order_fbf7e08fda14</t>
+  </si>
+  <si>
+    <t>14/3/2026, 10:45:40 pm</t>
+  </si>
+  <si>
+    <t>order_9c32a1dd8cf6</t>
+  </si>
+  <si>
+    <t>14/3/2026, 11:14:07 pm</t>
   </si>
   <si>
     <t>Committee</t>
@@ -1952,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:X43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3987,16 +4365,16 @@
         <v>239</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="F28" s="3">
+        <v>25</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>30</v>
@@ -4008,16 +4386,16 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="N28" s="3">
+        <v>250</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>30</v>
+        <v>243</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>235</v>
@@ -4026,7 +4404,7 @@
         <v>227</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>30</v>
@@ -4052,13 +4430,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>30</v>
@@ -4126,13 +4504,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>27</v>
@@ -4141,10 +4519,10 @@
         <v>23</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>30</v>
@@ -4156,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="M30" s="3" t="s">
         <v>32</v>
@@ -4165,7 +4543,7 @@
         <v>250</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>235</v>
@@ -4192,7 +4570,7 @@
         <v>30</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -4200,25 +4578,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F31" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>30</v>
@@ -4230,28 +4608,28 @@
         <v>0</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="M31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="N31" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>258</v>
+        <v>81</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="T31" s="3" t="s">
         <v>35</v>
@@ -4266,7 +4644,7 @@
         <v>30</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -4274,13 +4652,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>74</v>
+        <v>257</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>76</v>
+        <v>259</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>41</v>
@@ -4289,10 +4667,10 @@
         <v>20</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>78</v>
+        <v>261</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>30</v>
@@ -4304,34 +4682,34 @@
         <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>32</v>
       </c>
       <c r="N32" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>81</v>
+        <v>264</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="U32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>36</v>
@@ -4340,7 +4718,7 @@
         <v>30</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.25">
@@ -4348,25 +4726,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F33" s="3">
         <v>20</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>30</v>
@@ -4378,22 +4756,22 @@
         <v>0</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="N33" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>30</v>
@@ -4414,7 +4792,7 @@
         <v>30</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -4422,25 +4800,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F34" s="3">
         <v>20</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>30</v>
@@ -4452,22 +4830,22 @@
         <v>0</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="M34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="N34" s="3">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="P34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="R34" s="3" t="s">
         <v>30</v>
@@ -4488,7 +4866,673 @@
         <v>30</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>276</v>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="3">
+        <v>19</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" s="3">
+        <v>1</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="3">
+        <v>19</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="3">
+        <v>1</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="3">
+        <v>19</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="3">
+        <v>250</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="3">
+        <v>20</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K39" s="3">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="3">
+        <v>250</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X39" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="3">
+        <v>22</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="3">
+        <v>250</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="3">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="3">
+        <v>250</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="R41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="3">
+        <v>23</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="3">
+        <v>250</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="3">
+        <v>17</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" s="3">
+        <v>150</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -4500,7 +5544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4527,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -4551,10 +5595,10 @@
         <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>278</v>
+        <v>344</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>279</v>
+        <v>345</v>
       </c>
       <c r="L1" s="5" t="s">
         <v>8</v>
@@ -4607,7 +5651,7 @@
         <v>17</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>30</v>
@@ -4663,7 +5707,7 @@
         <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>30</v>
@@ -4719,7 +5763,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>30</v>
@@ -4775,7 +5819,7 @@
         <v>19</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>30</v>
@@ -4831,7 +5875,7 @@
         <v>20</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>30</v>
@@ -4887,7 +5931,7 @@
         <v>18</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>30</v>
@@ -4943,7 +5987,7 @@
         <v>17</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>30</v>
@@ -4999,7 +6043,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>30</v>
@@ -5034,28 +6078,28 @@
         <v>82</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>254</v>
+        <v>77</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>255</v>
+        <v>78</v>
       </c>
       <c r="I10" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>30</v>
@@ -5070,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>36</v>
@@ -5079,7 +6123,7 @@
         <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -5090,28 +6134,28 @@
         <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>76</v>
+        <v>295</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>77</v>
+        <v>296</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="I11" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>30</v>
@@ -5126,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>36</v>
@@ -5135,7 +6179,7 @@
         <v>36</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>261</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -5167,10 +6211,10 @@
         <v>17</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>30</v>
@@ -5223,10 +6267,10 @@
         <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>282</v>
+        <v>348</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>30</v>
@@ -5279,10 +6323,10 @@
         <v>30</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>30</v>
@@ -5335,10 +6379,10 @@
         <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>284</v>
+        <v>350</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>30</v>
@@ -5391,7 +6435,7 @@
         <v>17</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>30</v>
@@ -5447,7 +6491,7 @@
         <v>20</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>30</v>
@@ -5503,7 +6547,7 @@
         <v>19</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>30</v>
@@ -5541,7 +6585,7 @@
         <v>74</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>76</v>
@@ -5559,7 +6603,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>30</v>
@@ -5583,7 +6627,7 @@
         <v>36</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -5591,31 +6635,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>24</v>
+        <v>285</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>286</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>287</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>28</v>
+        <v>288</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>29</v>
+        <v>289</v>
       </c>
       <c r="I20" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>30</v>
@@ -5630,7 +6674,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>31</v>
+        <v>290</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>35</v>
@@ -5639,7 +6683,7 @@
         <v>36</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>37</v>
+        <v>292</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
@@ -5650,28 +6694,28 @@
         <v>34</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>204</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>206</v>
+        <v>28</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>207</v>
+        <v>29</v>
       </c>
       <c r="I21" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>30</v>
@@ -5686,7 +6730,7 @@
         <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>35</v>
@@ -5695,7 +6739,7 @@
         <v>36</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
@@ -5706,13 +6750,13 @@
         <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>27</v>
@@ -5721,13 +6765,13 @@
         <v>206</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I22" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>30</v>
@@ -5742,7 +6786,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>35</v>
@@ -5751,7 +6795,7 @@
         <v>36</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -5759,31 +6803,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>254</v>
+        <v>206</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>255</v>
+        <v>214</v>
       </c>
       <c r="I23" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>30</v>
@@ -5798,16 +6842,16 @@
         <v>0</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -5815,31 +6859,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>262</v>
+        <v>339</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>263</v>
+        <v>340</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>264</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>265</v>
+        <v>28</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>266</v>
+        <v>29</v>
       </c>
       <c r="I24" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>30</v>
@@ -5854,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>267</v>
+        <v>31</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>35</v>
@@ -5863,7 +6907,7 @@
         <v>36</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -5871,34 +6915,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>222</v>
+        <v>261</v>
       </c>
       <c r="I25" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>285</v>
+        <v>30</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>30</v>
@@ -5910,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="P25" s="3" t="s">
         <v>35</v>
@@ -5919,7 +6963,7 @@
         <v>36</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>228</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
@@ -5927,34 +6971,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="I26" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>285</v>
+        <v>30</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>30</v>
@@ -5966,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>233</v>
+        <v>278</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>35</v>
@@ -5975,7 +7019,7 @@
         <v>36</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
@@ -5986,31 +7030,31 @@
         <v>227</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>30</v>
+        <v>222</v>
+      </c>
+      <c r="I27" s="3">
+        <v>24</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>30</v>
@@ -6022,7 +7066,7 @@
         <v>0</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>30</v>
+        <v>223</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>35</v>
@@ -6031,7 +7075,7 @@
         <v>36</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
@@ -6042,31 +7086,31 @@
         <v>227</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>30</v>
+        <v>232</v>
+      </c>
+      <c r="I28" s="3">
+        <v>24</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>30</v>
@@ -6078,7 +7122,7 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="P28" s="3" t="s">
         <v>35</v>
@@ -6098,31 +7142,31 @@
         <v>227</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="I29" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>285</v>
+        <v>351</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>30</v>
@@ -6134,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>35</v>
@@ -6143,7 +7187,7 @@
         <v>36</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
@@ -6151,34 +7195,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>227</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="I30" s="3">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>30</v>
+        <v>351</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>30</v>
@@ -6190,7 +7234,7 @@
         <v>0</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="P30" s="3" t="s">
         <v>35</v>
@@ -6199,7 +7243,7 @@
         <v>36</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>47</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
@@ -6207,34 +7251,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>190</v>
+        <v>250</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="I31" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>30</v>
+        <v>351</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>30</v>
@@ -6246,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="O31" s="3" t="s">
-        <v>192</v>
+        <v>252</v>
       </c>
       <c r="P31" s="3" t="s">
         <v>35</v>
@@ -6255,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -6263,34 +7307,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>188</v>
+        <v>39</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>189</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>190</v>
+        <v>42</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="I32" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>281</v>
+        <v>346</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>286</v>
+        <v>30</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>30</v>
@@ -6302,7 +7346,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>35</v>
@@ -6311,7 +7355,7 @@
         <v>36</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
@@ -6319,34 +7363,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>196</v>
+        <v>308</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>198</v>
+        <v>301</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>199</v>
+        <v>302</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>30</v>
+        <v>304</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>30</v>
+        <v>305</v>
+      </c>
+      <c r="I33" s="3">
+        <v>19</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>286</v>
+        <v>30</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>30</v>
@@ -6358,16 +7402,16 @@
         <v>0</v>
       </c>
       <c r="O33" s="3" t="s">
-        <v>30</v>
+        <v>306</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>202</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -6375,31 +7419,31 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>218</v>
+        <v>310</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>222</v>
+        <v>313</v>
       </c>
       <c r="I34" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>30</v>
@@ -6414,16 +7458,16 @@
         <v>0</v>
       </c>
       <c r="O34" s="3" t="s">
-        <v>223</v>
+        <v>314</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>228</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
@@ -6431,31 +7475,31 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>229</v>
+        <v>317</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>231</v>
+        <v>319</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>232</v>
+        <v>320</v>
       </c>
       <c r="I35" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>30</v>
@@ -6470,16 +7514,16 @@
         <v>0</v>
       </c>
       <c r="O35" s="3" t="s">
-        <v>233</v>
+        <v>321</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>236</v>
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
@@ -6487,31 +7531,31 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>243</v>
+        <v>324</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>246</v>
+        <v>304</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="I36" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>30</v>
@@ -6526,16 +7570,16 @@
         <v>0</v>
       </c>
       <c r="O36" s="3" t="s">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>250</v>
+        <v>330</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
@@ -6543,31 +7587,31 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>226</v>
+        <v>308</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>270</v>
+        <v>331</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>272</v>
+        <v>333</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>273</v>
+        <v>335</v>
       </c>
       <c r="I37" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>30</v>
@@ -6582,16 +7626,16 @@
         <v>0</v>
       </c>
       <c r="O37" s="3" t="s">
-        <v>274</v>
+        <v>336</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>276</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
@@ -6599,31 +7643,31 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>66</v>
+        <v>188</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>67</v>
+        <v>189</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>30</v>
@@ -6638,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="O38" s="3" t="s">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>35</v>
@@ -6647,7 +7691,7 @@
         <v>36</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
@@ -6655,34 +7699,34 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>77</v>
+        <v>190</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="I39" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>30</v>
+        <v>352</v>
       </c>
       <c r="L39" s="3" t="s">
         <v>30</v>
@@ -6694,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="3" t="s">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="P39" s="3" t="s">
         <v>35</v>
@@ -6703,7 +7747,7 @@
         <v>36</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
@@ -6711,34 +7755,34 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I40" s="3">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>30</v>
+        <v>352</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>30</v>
@@ -6750,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="O40" s="3" t="s">
-        <v>97</v>
+        <v>30</v>
       </c>
       <c r="P40" s="3" t="s">
         <v>35</v>
@@ -6759,7 +7803,7 @@
         <v>36</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
@@ -6767,31 +7811,31 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>72</v>
+        <v>353</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>100</v>
+        <v>281</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>101</v>
+        <v>282</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I41" s="3">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>30</v>
@@ -6800,22 +7844,22 @@
         <v>30</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>30</v>
+        <v>283</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>107</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
@@ -6823,31 +7867,31 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>109</v>
+        <v>219</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="I42" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>30</v>
@@ -6862,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
-        <v>113</v>
+        <v>223</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>35</v>
@@ -6871,7 +7915,7 @@
         <v>36</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>115</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
@@ -6879,31 +7923,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>116</v>
+        <v>229</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>117</v>
+        <v>230</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>118</v>
+        <v>231</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>119</v>
+        <v>221</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>120</v>
+        <v>232</v>
       </c>
       <c r="I43" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>30</v>
@@ -6918,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="3" t="s">
-        <v>121</v>
+        <v>233</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>35</v>
@@ -6927,7 +7971,7 @@
         <v>36</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>123</v>
+        <v>236</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
@@ -6935,31 +7979,31 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>126</v>
+        <v>239</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>128</v>
+        <v>241</v>
       </c>
       <c r="I44" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>30</v>
@@ -6974,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>129</v>
+        <v>242</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>35</v>
@@ -6983,7 +8027,7 @@
         <v>36</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>131</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
@@ -6991,31 +8035,31 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>140</v>
+        <v>247</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>142</v>
+        <v>249</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>143</v>
+        <v>250</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="I45" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>30</v>
@@ -7030,7 +8074,7 @@
         <v>0</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>35</v>
@@ -7039,7 +8083,7 @@
         <v>36</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
@@ -7047,31 +8091,31 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>165</v>
+        <v>267</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>103</v>
+        <v>221</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="I46" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>30</v>
@@ -7086,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="O46" s="3" t="s">
-        <v>168</v>
+        <v>270</v>
       </c>
       <c r="P46" s="3" t="s">
         <v>35</v>
@@ -7095,7 +8139,7 @@
         <v>36</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
@@ -7106,28 +8150,28 @@
         <v>72</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="I47" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>30</v>
@@ -7142,16 +8186,520 @@
         <v>0</v>
       </c>
       <c r="O47" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>36</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>261</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I48" s="3">
+        <v>20</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R48" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I49" s="3">
+        <v>22</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R49" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I50" s="3">
+        <v>19</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I51" s="3">
+        <v>18</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I52" s="3">
+        <v>19</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
+        <v>52</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I53" s="3">
+        <v>18</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="I54" s="3">
+        <v>21</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" s="3">
+        <v>0</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>54</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I55" s="3">
+        <v>18</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N55" s="3">
+        <v>0</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R55" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" s="3">
+        <v>20</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N56" s="3">
+        <v>0</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -7163,7 +8711,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P60"/>
+  <dimension ref="A1:P83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -7189,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>287</v>
+        <v>354</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>1</v>
@@ -7219,10 +8767,10 @@
         <v>8</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>288</v>
+        <v>355</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>289</v>
+        <v>356</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>12</v>
@@ -7231,7 +8779,7 @@
         <v>14</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>290</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -7239,13 +8787,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>339</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>340</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>26</v>
@@ -7275,13 +8823,13 @@
         <v>150</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>30</v>
+        <v>341</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>293</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -7289,49 +8837,49 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>294</v>
+        <v>360</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>295</v>
+        <v>339</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>297</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G3" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>298</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>299</v>
+        <v>29</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>300</v>
+        <v>31</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="M3" s="3">
-        <v>251</v>
+        <v>150</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -7339,7 +8887,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>24</v>
@@ -7375,13 +8923,13 @@
         <v>150</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>304</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -7389,16 +8937,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>305</v>
+        <v>364</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>251</v>
+        <v>365</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>252</v>
+        <v>366</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>253</v>
+        <v>367</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>27</v>
@@ -7407,31 +8955,31 @@
         <v>19</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>254</v>
+        <v>368</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>255</v>
+        <v>369</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>256</v>
+        <v>370</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>258</v>
+        <v>371</v>
       </c>
       <c r="M5" s="3">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -7439,40 +8987,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>307</v>
+        <v>373</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G6" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M6" s="3">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>32</v>
@@ -7481,7 +9029,7 @@
         <v>30</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>308</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -7489,49 +9037,49 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>309</v>
+        <v>375</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>310</v>
+        <v>376</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="3">
+        <v>19</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="M7" s="3">
-        <v>800</v>
-      </c>
       <c r="N7" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -7539,49 +9087,49 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>310</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>311</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>312</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3">
+        <v>19</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="M8" s="3">
-        <v>3152</v>
-      </c>
       <c r="N8" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>320</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -7589,49 +9137,49 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>321</v>
+        <v>381</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>382</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>383</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>50</v>
+        <v>384</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="3">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>28</v>
+        <v>385</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>51</v>
+        <v>386</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>52</v>
+        <v>387</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>54</v>
+        <v>388</v>
       </c>
       <c r="M9" s="3">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -7639,49 +9187,49 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>324</v>
+        <v>382</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>325</v>
+        <v>383</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>326</v>
+        <v>384</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G10" s="3">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>254</v>
+        <v>385</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>328</v>
+        <v>387</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>34</v>
+        <v>391</v>
       </c>
       <c r="M10" s="3">
-        <v>150</v>
+        <v>3152</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>329</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -7689,49 +9237,49 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>330</v>
+        <v>393</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>251</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>252</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>253</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G11" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>254</v>
+        <v>28</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>255</v>
+        <v>51</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>256</v>
+        <v>52</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>258</v>
+        <v>54</v>
       </c>
       <c r="M11" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>331</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -7739,16 +9287,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>396</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>57</v>
+        <v>397</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>58</v>
+        <v>398</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>27</v>
@@ -7757,31 +9305,31 @@
         <v>19</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>59</v>
+        <v>296</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>60</v>
+        <v>399</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>61</v>
+        <v>400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="M12" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>333</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -7789,49 +9337,49 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>334</v>
+        <v>402</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>65</v>
+        <v>376</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>66</v>
+        <v>294</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G13" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>68</v>
+        <v>296</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>69</v>
+        <v>289</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>70</v>
+        <v>377</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>72</v>
+        <v>264</v>
       </c>
       <c r="M13" s="3">
         <v>1</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>335</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -7839,49 +9387,49 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>336</v>
+        <v>404</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G14" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="M14" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>337</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -7889,7 +9437,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>338</v>
+        <v>406</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>65</v>
@@ -7925,13 +9473,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -7939,49 +9487,49 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>252</v>
+        <v>66</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G16" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>254</v>
+        <v>68</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>255</v>
+        <v>69</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>256</v>
+        <v>70</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M16" s="3">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
@@ -7989,49 +9537,49 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G17" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>343</v>
+        <v>72</v>
       </c>
       <c r="M17" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>344</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -8039,49 +9587,49 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>345</v>
+        <v>412</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>347</v>
+        <v>294</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>349</v>
+        <v>296</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="M18" s="3">
         <v>250</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>352</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
@@ -8089,49 +9637,49 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>353</v>
+        <v>414</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G19" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="M19" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>354</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
@@ -8139,49 +9687,49 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>355</v>
+        <v>417</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>251</v>
+        <v>418</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>252</v>
+        <v>419</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>253</v>
+        <v>420</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G20" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>254</v>
+        <v>421</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="M20" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>356</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
@@ -8189,31 +9737,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>357</v>
+        <v>425</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>251</v>
+        <v>84</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>252</v>
+        <v>85</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G21" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>254</v>
+        <v>87</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>255</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>256</v>
+        <v>89</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>30</v>
@@ -8225,13 +9773,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>358</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
@@ -8239,31 +9787,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>359</v>
+        <v>427</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>87</v>
+        <v>296</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>88</v>
+        <v>289</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>30</v>
@@ -8275,13 +9823,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>360</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
@@ -8289,31 +9837,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>361</v>
+        <v>429</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>85</v>
+        <v>294</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>87</v>
+        <v>296</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>88</v>
+        <v>289</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>89</v>
+        <v>377</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>30</v>
@@ -8331,7 +9879,7 @@
         <v>30</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>362</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
@@ -8339,49 +9887,49 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>363</v>
+        <v>431</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G24" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M24" s="3">
         <v>1</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>364</v>
+        <v>432</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
@@ -8389,37 +9937,37 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>365</v>
+        <v>433</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G25" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="M25" s="3">
         <v>1</v>
@@ -8431,7 +9979,7 @@
         <v>30</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>366</v>
+        <v>434</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
@@ -8439,7 +9987,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>92</v>
@@ -8475,13 +10023,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>368</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
@@ -8489,31 +10037,31 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>369</v>
+        <v>437</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>30</v>
@@ -8531,7 +10079,7 @@
         <v>30</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>370</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
@@ -8539,31 +10087,31 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G28" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>30</v>
@@ -8575,13 +10123,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>372</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
@@ -8589,16 +10137,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>373</v>
+        <v>441</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>41</v>
@@ -8607,13 +10155,13 @@
         <v>19</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>30</v>
@@ -8631,7 +10179,7 @@
         <v>30</v>
       </c>
       <c r="P29" s="3" t="s">
-        <v>374</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -8639,31 +10187,31 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>375</v>
+        <v>443</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G30" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>30</v>
@@ -8675,13 +10223,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>376</v>
+        <v>444</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
@@ -8689,31 +10237,31 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>377</v>
+        <v>445</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G31" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>30</v>
@@ -8731,7 +10279,7 @@
         <v>30</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>378</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
@@ -8739,13 +10287,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>92</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>380</v>
+        <v>93</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>94</v>
@@ -8775,13 +10323,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P32" s="3" t="s">
-        <v>381</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
@@ -8789,37 +10337,37 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G33" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M33" s="3">
         <v>1</v>
@@ -8831,7 +10379,7 @@
         <v>30</v>
       </c>
       <c r="P33" s="3" t="s">
-        <v>383</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
@@ -8839,49 +10387,49 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>384</v>
+        <v>451</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>133</v>
+        <v>452</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G34" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>137</v>
+        <v>97</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M34" s="3">
         <v>1</v>
       </c>
       <c r="N34" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O34" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>385</v>
+        <v>453</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
@@ -8889,7 +10437,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>386</v>
+        <v>454</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>132</v>
@@ -8925,13 +10473,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>387</v>
+        <v>455</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
@@ -8939,7 +10487,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>132</v>
@@ -8975,13 +10523,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>389</v>
+        <v>457</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
@@ -8989,49 +10537,49 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>390</v>
+        <v>458</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G37" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="M37" s="3">
         <v>1</v>
       </c>
       <c r="N37" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O37" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>391</v>
+        <v>459</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -9039,40 +10587,40 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>392</v>
+        <v>460</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G38" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="K38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>393</v>
+        <v>81</v>
       </c>
       <c r="M38" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3" t="s">
         <v>32</v>
@@ -9081,7 +10629,7 @@
         <v>30</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
@@ -9089,31 +10637,31 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>395</v>
+        <v>462</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G39" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>30</v>
@@ -9125,13 +10673,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O39" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>396</v>
+        <v>463</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.25">
@@ -9139,49 +10687,49 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>397</v>
+        <v>464</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G40" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>72</v>
+        <v>465</v>
       </c>
       <c r="M40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O40" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>398</v>
+        <v>466</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
@@ -9189,7 +10737,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>399</v>
+        <v>467</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>164</v>
@@ -9225,13 +10773,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>400</v>
+        <v>468</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -9239,49 +10787,49 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>401</v>
+        <v>469</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>41</v>
       </c>
       <c r="G42" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>402</v>
+        <v>72</v>
       </c>
       <c r="M42" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N42" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>403</v>
+        <v>470</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.25">
@@ -9289,49 +10837,49 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>404</v>
+        <v>471</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>405</v>
+        <v>164</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>406</v>
+        <v>165</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>407</v>
+        <v>166</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G43" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>408</v>
+        <v>103</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>409</v>
+        <v>167</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>410</v>
+        <v>168</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>411</v>
+        <v>72</v>
       </c>
       <c r="M43" s="3">
-        <v>750</v>
+        <v>1</v>
       </c>
       <c r="N43" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.25">
@@ -9339,49 +10887,49 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>413</v>
+        <v>473</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>251</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G44" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>254</v>
+        <v>174</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>256</v>
+        <v>176</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="M44" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N44" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>414</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.25">
@@ -9389,16 +10937,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>415</v>
+        <v>476</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>251</v>
+        <v>477</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>252</v>
+        <v>478</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>253</v>
+        <v>479</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>27</v>
@@ -9407,31 +10955,31 @@
         <v>19</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>254</v>
+        <v>480</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>255</v>
+        <v>481</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>256</v>
+        <v>482</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>258</v>
+        <v>483</v>
       </c>
       <c r="M45" s="3">
-        <v>1</v>
+        <v>750</v>
       </c>
       <c r="N45" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>416</v>
+        <v>484</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.25">
@@ -9439,16 +10987,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>417</v>
+        <v>485</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>251</v>
+        <v>376</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>27</v>
@@ -9457,31 +11005,31 @@
         <v>19</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>256</v>
+        <v>377</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="M46" s="3">
         <v>1</v>
       </c>
       <c r="N46" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O46" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>418</v>
+        <v>486</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.25">
@@ -9489,16 +11037,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>419</v>
+        <v>487</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>251</v>
+        <v>376</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>27</v>
@@ -9507,31 +11055,31 @@
         <v>19</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>256</v>
+        <v>377</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M47" s="3">
         <v>1</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>420</v>
+        <v>488</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.25">
@@ -9539,16 +11087,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>421</v>
+        <v>489</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>251</v>
+        <v>376</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>27</v>
@@ -9557,31 +11105,31 @@
         <v>19</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>422</v>
+        <v>289</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>423</v>
+        <v>377</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M48" s="3">
         <v>1</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
@@ -9589,49 +11137,49 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>187</v>
+        <v>376</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>188</v>
+        <v>294</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G49" s="3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>191</v>
+        <v>289</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>192</v>
+        <v>377</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="M49" s="3">
-        <v>1100</v>
+        <v>1</v>
       </c>
       <c r="N49" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>426</v>
+        <v>492</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -9639,16 +11187,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>203</v>
+        <v>376</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>204</v>
+        <v>294</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>205</v>
+        <v>295</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>27</v>
@@ -9657,31 +11205,31 @@
         <v>19</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>206</v>
+        <v>385</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>207</v>
+        <v>494</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>208</v>
+        <v>495</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="M50" s="3">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="N50" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O50" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
@@ -9689,40 +11237,40 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>429</v>
+        <v>497</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G51" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="M51" s="3">
-        <v>150</v>
+        <v>1100</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>32</v>
@@ -9731,7 +11279,7 @@
         <v>30</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>430</v>
+        <v>498</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -9739,16 +11287,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>431</v>
+        <v>499</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>432</v>
+        <v>203</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>433</v>
+        <v>204</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>434</v>
+        <v>205</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>27</v>
@@ -9757,13 +11305,13 @@
         <v>19</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>435</v>
+        <v>206</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>436</v>
+        <v>207</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>437</v>
+        <v>208</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>30</v>
@@ -9775,13 +11323,13 @@
         <v>150</v>
       </c>
       <c r="N52" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>438</v>
+        <v>500</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
@@ -9789,40 +11337,40 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>439</v>
+        <v>501</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G53" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="M53" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="N53" s="3" t="s">
         <v>32</v>
@@ -9831,7 +11379,7 @@
         <v>30</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>440</v>
+        <v>502</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
@@ -9839,49 +11387,49 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>441</v>
+        <v>503</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>442</v>
+        <v>504</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>230</v>
+        <v>505</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>231</v>
+        <v>506</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G54" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>221</v>
+        <v>507</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>232</v>
+        <v>508</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>233</v>
+        <v>509</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>226</v>
+        <v>34</v>
       </c>
       <c r="M54" s="3">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="N54" s="3" t="s">
-        <v>32</v>
+        <v>362</v>
       </c>
       <c r="O54" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>443</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -9889,31 +11437,31 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>444</v>
+        <v>511</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>445</v>
+        <v>218</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G55" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>30</v>
@@ -9931,7 +11479,7 @@
         <v>30</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>446</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
@@ -9939,49 +11487,49 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>447</v>
+        <v>513</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>448</v>
+        <v>514</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>449</v>
+        <v>230</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>450</v>
+        <v>231</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G56" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>451</v>
+        <v>221</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>452</v>
+        <v>232</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>453</v>
+        <v>233</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="M56" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="N56" s="3" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="O56" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>454</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
@@ -9989,40 +11537,40 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>455</v>
+        <v>516</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>262</v>
+        <v>517</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G57" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="M57" s="3">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>32</v>
@@ -10031,7 +11579,7 @@
         <v>30</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>456</v>
+        <v>518</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
@@ -10039,49 +11587,49 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>457</v>
+        <v>519</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>458</v>
+        <v>273</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>459</v>
+        <v>274</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>460</v>
+        <v>275</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G58" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>461</v>
+        <v>277</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>462</v>
+        <v>278</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>463</v>
+        <v>264</v>
       </c>
       <c r="M58" s="3">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>464</v>
+        <v>520</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
@@ -10089,40 +11637,40 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>465</v>
+        <v>521</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G59" s="3">
         <v>20</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="M59" s="3">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>32</v>
@@ -10131,7 +11679,7 @@
         <v>30</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>466</v>
+        <v>522</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
@@ -10139,49 +11687,1199 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>467</v>
+        <v>523</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>468</v>
+        <v>524</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G60" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>471</v>
+        <v>296</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>473</v>
+        <v>528</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>63</v>
+        <v>529</v>
       </c>
       <c r="M60" s="3">
         <v>250</v>
       </c>
       <c r="N60" s="3" t="s">
-        <v>292</v>
+        <v>362</v>
       </c>
       <c r="O60" s="3" t="s">
         <v>30</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>474</v>
+        <v>530</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="3">
+        <v>60</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" s="3">
+        <v>20</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M61" s="3">
+        <v>250</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="3">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" s="3">
+        <v>18</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="M62" s="3">
+        <v>250</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="3">
+        <v>62</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G63" s="3">
+        <v>18</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="M63" s="3">
+        <v>1</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="3">
+        <v>63</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" s="3">
+        <v>22</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M64" s="3">
+        <v>250</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P64" s="3" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="3">
+        <v>64</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="3">
+        <v>19</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M65" s="3">
+        <v>1</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="3">
+        <v>65</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="3">
+        <v>19</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L66" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M66" s="3">
+        <v>1</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="3">
+        <v>66</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" s="3">
+        <v>20</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M67" s="3">
+        <v>1</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="3">
+        <v>67</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" s="3">
+        <v>19</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L68" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M68" s="3">
+        <v>1</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
+        <v>68</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" s="3">
+        <v>19</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L69" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="M69" s="3">
+        <v>1</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="3">
+        <v>69</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" s="3">
+        <v>19</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M70" s="3">
+        <v>1</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="3">
+        <v>70</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" s="3">
+        <v>25</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M71" s="3">
+        <v>250</v>
+      </c>
+      <c r="N71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P71" s="3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="3">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G72" s="3">
+        <v>24</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M72" s="3">
+        <v>250</v>
+      </c>
+      <c r="N72" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="3">
+        <v>72</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G73" s="3">
+        <v>19</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M73" s="3">
+        <v>1</v>
+      </c>
+      <c r="N73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P73" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="3">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G74" s="3">
+        <v>19</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M74" s="3">
+        <v>1</v>
+      </c>
+      <c r="N74" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P74" s="3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="3">
+        <v>74</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G75" s="3">
+        <v>19</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M75" s="3">
+        <v>1</v>
+      </c>
+      <c r="N75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P75" s="3" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="3">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G76" s="3">
+        <v>19</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M76" s="3">
+        <v>250</v>
+      </c>
+      <c r="N76" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="3">
+        <v>76</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" s="3">
+        <v>19</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M77" s="3">
+        <v>250</v>
+      </c>
+      <c r="N77" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P77" s="3" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G78" s="3">
+        <v>19</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M78" s="3">
+        <v>250</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P78" s="3" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A79" s="3">
+        <v>78</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" s="3">
+        <v>20</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M79" s="3">
+        <v>250</v>
+      </c>
+      <c r="N79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O79" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P79" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A80" s="3">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" s="3">
+        <v>22</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M80" s="3">
+        <v>250</v>
+      </c>
+      <c r="N80" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P80" s="3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A81" s="3">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G81" s="3">
+        <v>22</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M81" s="3">
+        <v>250</v>
+      </c>
+      <c r="N81" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="3">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G82" s="3">
+        <v>22</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L82" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M82" s="3">
+        <v>250</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P82" s="3" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="3">
+        <v>82</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G83" s="3">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="M83" s="3">
+        <v>250</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -10203,21 +12901,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>475</v>
+        <v>601</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>476</v>
+        <v>602</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>477</v>
+        <v>603</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>478</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>479</v>
+        <v>605</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -10226,12 +12924,12 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>481</v>
+        <v>607</v>
       </c>
       <c r="B3" s="3">
         <v>46</v>
@@ -10240,12 +12938,12 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>482</v>
+        <v>608</v>
       </c>
       <c r="B4" s="3">
         <v>25</v>
@@ -10254,12 +12952,12 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>483</v>
+        <v>609</v>
       </c>
       <c r="B5" s="3">
         <v>7</v>
@@ -10268,12 +12966,12 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>484</v>
+        <v>610</v>
       </c>
       <c r="B6" s="3">
         <v>15</v>
@@ -10282,12 +12980,12 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>485</v>
+        <v>611</v>
       </c>
       <c r="B7" s="3">
         <v>21</v>
@@ -10296,12 +12994,12 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>486</v>
+        <v>612</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -10310,12 +13008,12 @@
         <v>0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>487</v>
+        <v>613</v>
       </c>
       <c r="B9" s="3">
         <v>26</v>
@@ -10324,12 +13022,12 @@
         <v>0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>488</v>
+        <v>614</v>
       </c>
       <c r="B10" s="3">
         <v>14</v>
@@ -10338,12 +13036,12 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>489</v>
+        <v>615</v>
       </c>
       <c r="B11" s="3">
         <v>16</v>
@@ -10352,12 +13050,12 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>490</v>
+        <v>616</v>
       </c>
       <c r="B12" s="3">
         <v>22</v>
@@ -10366,12 +13064,12 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>491</v>
+        <v>617</v>
       </c>
       <c r="B13" s="3">
         <v>40</v>
@@ -10380,12 +13078,12 @@
         <v>0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>492</v>
+        <v>618</v>
       </c>
       <c r="B14" s="3">
         <v>26</v>
@@ -10394,12 +13092,12 @@
         <v>0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>493</v>
+        <v>619</v>
       </c>
       <c r="B15" s="3">
         <v>16</v>
@@ -10408,12 +13106,12 @@
         <v>0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>494</v>
+        <v>620</v>
       </c>
       <c r="B16" s="3">
         <v>15</v>
@@ -10422,12 +13120,12 @@
         <v>0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>495</v>
+        <v>621</v>
       </c>
       <c r="B17" s="3">
         <v>19</v>
@@ -10436,12 +13134,12 @@
         <v>0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>496</v>
+        <v>622</v>
       </c>
       <c r="B18" s="3">
         <v>3</v>
@@ -10450,23 +13148,23 @@
         <v>0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>480</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:1" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>497</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" spans="1:3" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>498</v>
+        <v>624</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>475</v>
+        <v>601</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>499</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>
